--- a/python/input.xlsx
+++ b/python/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/natomanzolli/Documents/GitHub/EvTransitMatsim/python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0F7A0E-E42F-6043-84A2-88EF465A785D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDD54D6-6B06-074D-B3D6-A22ACA6861BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1379,59 +1379,37 @@
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A98" s="2">
-        <v>9.6196376021798397E-2</v>
-      </c>
+      <c r="A98" s="2"/>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A99" s="2">
-        <v>9.6196376021798397E-2</v>
-      </c>
+      <c r="A99" s="2"/>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A100" s="2">
-        <v>9.6196376021798397E-2</v>
-      </c>
+      <c r="A100" s="2"/>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A101" s="2">
-        <v>9.6196376021798397E-2</v>
-      </c>
+      <c r="A101" s="2"/>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A102" s="2">
-        <v>8.8765994550408706E-2</v>
-      </c>
+      <c r="A102" s="2"/>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A103" s="2">
-        <v>8.8765994550408706E-2</v>
-      </c>
+      <c r="A103" s="2"/>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A104" s="2">
-        <v>8.8765994550408706E-2</v>
-      </c>
+      <c r="A104" s="2"/>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A105" s="2">
-        <v>8.8765994550408706E-2</v>
-      </c>
+      <c r="A105" s="2"/>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A106" s="2">
-        <v>8.4496621253405998E-2</v>
-      </c>
+      <c r="A106" s="2"/>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A107" s="2">
-        <v>8.4496621253405998E-2</v>
-      </c>
+      <c r="A107" s="2"/>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A108" s="2">
-        <v>8.4496621253405998E-2</v>
-      </c>
+      <c r="A108" s="2"/>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
